--- a/data/modelling/atribucion/tv/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/tv/df_attr_values_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32254</v>
+        <v>31949</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>294</v>
+        <v>229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3418910336460161</v>
+        <v>0.1829777427633414</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86749</v>
+        <v>88999</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -476,15 +476,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2008443515841948</v>
+        <v>-0.4547469193577611</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>48799</v>
+        <v>47662</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -492,15 +492,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7368121703866177</v>
+        <v>-0.3081250675912776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61022</v>
+        <v>57949</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -508,15 +508,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.434875768309843</v>
+        <v>0.3388544249063448</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40428.5</v>
+        <v>39423.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -524,15 +524,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.249882962621929</v>
+        <v>-1.759106974602828</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107769.5</v>
+        <v>111499.5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -540,15 +540,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D7" t="n">
-        <v>1.055700418637401</v>
+        <v>1.477153086194475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74207.5</v>
+        <v>73943.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -559,12 +559,12 @@
         <v>216</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7511994598459381</v>
+        <v>0.5229937076877108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>153499</v>
+        <v>153999</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>0.641063313392762</v>
+        <v>0.6958457843268518</v>
       </c>
     </row>
     <row r="11">
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.226819941774361</v>
+        <v>-0.0283558348946911</v>
       </c>
     </row>
     <row r="12">
@@ -627,7 +627,7 @@
         <v>164</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1851767947028444</v>
+        <v>0.2777658505116923</v>
       </c>
     </row>
     <row r="13">
@@ -645,7 +645,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1599615181255915</v>
+        <v>-0.05278218811277479</v>
       </c>
     </row>
     <row r="14">
@@ -663,7 +663,7 @@
         <v>123</v>
       </c>
       <c r="D14" t="n">
-        <v>1.331201567273542</v>
+        <v>1.328751000157634</v>
       </c>
     </row>
     <row r="15">
@@ -681,7 +681,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.233112217386216</v>
+        <v>-0.1195062105462084</v>
       </c>
     </row>
     <row r="16">
@@ -699,7 +699,7 @@
         <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6027051453102281</v>
+        <v>0.660668652045552</v>
       </c>
     </row>
     <row r="17">
@@ -749,7 +749,7 @@
         <v>181</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08866749998926694</v>
+        <v>0.1892600538008133</v>
       </c>
     </row>
     <row r="20">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D21" t="n">
-        <v>1.133197496376155</v>
+        <v>1.155834493391884</v>
       </c>
     </row>
     <row r="22">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" t="n">
-        <v>1.40880596711158</v>
+        <v>1.406208517972415</v>
       </c>
     </row>
     <row r="24">
@@ -835,7 +835,7 @@
         <v>70</v>
       </c>
       <c r="D24" t="n">
-        <v>1.111464417109521</v>
+        <v>1.106942236705434</v>
       </c>
     </row>
     <row r="25">
@@ -853,7 +853,7 @@
         <v>45</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2508681749482898</v>
+        <v>-0.1357022130817121</v>
       </c>
     </row>
     <row r="26">
@@ -887,7 +887,7 @@
         <v>57</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1404883042147423</v>
+        <v>0.2212715241358621</v>
       </c>
     </row>
     <row r="28">
@@ -921,7 +921,7 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9920167003350246</v>
+        <v>-0.811736910415498</v>
       </c>
     </row>
     <row r="30">
@@ -939,7 +939,7 @@
         <v>25</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.46094836726076</v>
+        <v>-1.239470443791885</v>
       </c>
     </row>
     <row r="31">
@@ -957,13 +957,13 @@
         <v>38</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.476806341974886</v>
+        <v>-1.25393521133709</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Admiral</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -972,14 +972,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.587261070548225</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Skyworth</t>
+          <t>Kodak</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -988,14 +990,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-1.813798030320057</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Admiral</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1004,16 +1008,14 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-1.842237243675517</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kodak</t>
+          <t>Skyworth</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1022,14 +1024,14 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Top House</t>
+          <t>Hyundai Electronics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1043,40 +1045,40 @@
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>812.8</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Top House</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.3404822513704385</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>1270</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CMB</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>933</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.009285272495861</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>609.5999999999999</v>
+        <v>812.8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1084,15 +1086,15 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>153</v>
+        <v>1148</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.177715161517086</v>
+        <v>0.325376379680352</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1092.2</v>
+        <v>1270</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1100,15 +1102,15 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>771</v>
+        <v>935</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8891755499083864</v>
+        <v>0.9854277527009757</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1397</v>
+        <v>609.5999999999999</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1116,15 +1118,15 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7917027908863392</v>
+        <v>-1.185259289103636</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1066.8</v>
+        <v>1092.2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1132,15 +1134,15 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>89</v>
+        <v>775</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.34137468538998</v>
+        <v>0.8717397059260841</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>990.5999999999999</v>
+        <v>1397</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1148,13 +1150,15 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>241</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8498665709890004</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1651</v>
+        <v>1066.8</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1162,13 +1166,15 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.329799537453058</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1016</v>
+        <v>990.5999999999999</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1176,15 +1182,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>177</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-0.5115560177539593</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1524</v>
+        <v>1651</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1192,13 +1196,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1778</v>
+        <v>1016</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1206,13 +1210,15 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>178</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.5173515827397187</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1905</v>
+        <v>1524</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1220,64 +1226,56 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>1473.2</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C50" t="n">
         <v>51</v>
       </c>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Tipo de resolución</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1149</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-1.096066360902925</v>
-      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>4K</t>
-        </is>
+      <c r="A51" t="n">
+        <v>1905</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1235</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.862642302017834</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full HD</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1286,16 +1284,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>871</v>
+        <v>1152</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2334240588850897</v>
+        <v>-1.105997607225658</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4K UHD</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1304,14 +1302,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>1251</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.8403608915930291</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FHD</t>
+          <t>Full HD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1320,105 +1320,107 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>876</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.2656367156326264</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>4K UHD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1366x768</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>1366 x 768 px</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C57" t="n">
         <v>0</v>
       </c>
-      <c r="D55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>190</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Brillo</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>401</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.8747190818036414</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>275</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Brillo</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>295</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.8758666909216728</v>
-      </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>315</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FHD</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brillo</t>
+          <t>Tipo de resolución</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>105</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-1.560855943805509</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>255</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>UHD</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Brillo</t>
+          <t>Tipo de resolución</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>203</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.01284636058775577</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>230</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HD ready</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Brillo</t>
+          <t>Tipo de resolución</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>219</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.1768834683320485</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1432,10 +1434,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8979585012223082</v>
+        <v>0.9225320911808448</v>
       </c>
     </row>
     <row r="62">
@@ -1453,7 +1455,7 @@
         <v>134</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.929412601831543</v>
+        <v>-1.924122208415359</v>
       </c>
     </row>
     <row r="63">
@@ -1471,7 +1473,7 @@
         <v>41</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3410919422726992</v>
+        <v>-0.3435489611394745</v>
       </c>
     </row>
     <row r="64">
@@ -1489,7 +1491,7 @@
         <v>716</v>
       </c>
       <c r="D64" t="n">
-        <v>1.697971826757542</v>
+        <v>1.693702176774144</v>
       </c>
     </row>
     <row r="65">
@@ -1507,7 +1509,7 @@
         <v>78</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.2242167886245141</v>
+        <v>-0.2272438938875703</v>
       </c>
     </row>
     <row r="66">
@@ -1525,7 +1527,7 @@
         <v>41</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.05553219073428552</v>
+        <v>-0.0593820952965738</v>
       </c>
     </row>
     <row r="67">
@@ -1543,13 +1545,13 @@
         <v>33</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3600569674675641</v>
+        <v>-0.3624214799073424</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>webOS</t>
+          <t>Android Oreo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1558,16 +1560,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2330082601708968</v>
+        <v>1.001015270956938</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Android Oreo</t>
+          <t>webOS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1576,16 +1578,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D69" t="n">
-        <v>1.010062869200484</v>
+        <v>-0.2359924829377555</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Xmart UI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1594,14 +1596,14 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Xmart UI</t>
+          <t>Android Pie</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1610,14 +1612,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>14</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.4645384173278526</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Android Pie</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1626,11 +1630,9 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>47</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-0.4626744460788311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1642,10 +1644,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2294144173559099</v>
+        <v>0.2310754830078264</v>
       </c>
     </row>
     <row r="74">
@@ -1661,7 +1663,7 @@
         <v>79</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.7163753659970231</v>
+        <v>-0.71370367242568</v>
       </c>
     </row>
     <row r="75">
@@ -1677,7 +1679,7 @@
         <v>30</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4468783250847376</v>
+        <v>0.4381082511161873</v>
       </c>
     </row>
     <row r="76">
@@ -1693,7 +1695,7 @@
         <v>55</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8644657321294993</v>
+        <v>0.8670039470360807</v>
       </c>
     </row>
     <row r="77">
@@ -1709,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8422745404714442</v>
+        <v>0.8448146290961597</v>
       </c>
     </row>
     <row r="78">
@@ -1725,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.666657649044567</v>
+        <v>-1.667298637830574</v>
       </c>
     </row>
     <row r="79">
@@ -1752,10 +1754,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8179866286416088</v>
+        <v>0.7760802674832891</v>
       </c>
     </row>
     <row r="81">
@@ -1768,10 +1770,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2968206884608428</v>
+        <v>0.5908421040603133</v>
       </c>
     </row>
     <row r="82">
@@ -1787,7 +1789,7 @@
         <v>330</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.114807317102452</v>
+        <v>0.06298594617374244</v>
       </c>
     </row>
     <row r="83">
@@ -1802,7 +1804,9 @@
       <c r="C83" t="n">
         <v>46</v>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>-1.429908317717345</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1845,228 +1849,6 @@
         <v>1</v>
       </c>
       <c r="D86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>1200:1</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>321</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0.9886694045195107</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>4000:1</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>374</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1.005759799543143</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>3000:1</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>274</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.8054030135553765</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>5000.1</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>5000:1</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>149</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0.2614114407766366</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Mega contraste</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>200000:1</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>78</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-0.6836290247937187</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>5000.3</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>6000:1</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2000:1</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>48</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-1.195726929501978</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>5000.2</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>4500:1</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>18</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2800:1</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Relación de contraste</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>48</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-1.181887704098969</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/modelling/atribucion/tv/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/tv/df_attr_values_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31949</v>
+        <v>106999</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1829777427633414</v>
+        <v>-0.8701611836201959</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88999</v>
+        <v>65739</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -476,15 +476,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4547469193577611</v>
+        <v>0.849566187897854</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47662</v>
+        <v>38468.5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -492,15 +492,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3081250675912776</v>
+        <v>0.3838895285317757</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57949</v>
+        <v>53048.5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -508,15 +508,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>339</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3388544249063448</v>
+        <v>0.3459012026978988</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>39423.5</v>
+        <v>80849</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -524,15 +524,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>314</v>
+        <v>248</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.759106974602828</v>
+        <v>0.7479914263107726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111499.5</v>
+        <v>92911</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -540,15 +540,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="D7" t="n">
-        <v>1.477153086194475</v>
+        <v>0.7049315310858165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73943.5</v>
+        <v>129994.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -556,15 +556,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5229937076877108</v>
+        <v>0.7652905704200198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>153999</v>
+        <v>17561</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -572,104 +572,90 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6171398473742488</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Noblex</t>
-        </is>
+      <c r="A10" t="n">
+        <v>45400</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6958457843268518</v>
+        <v>-0.02323040065098755</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
+      <c r="A11" t="n">
+        <v>159499</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0283558348946911</v>
+        <v>-2.287039015298706</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
+      <c r="A12" t="n">
+        <v>212499.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>164</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2777658505116923</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Telefunken</t>
-        </is>
+      <c r="A13" t="n">
+        <v>324999.5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.05278218811277479</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Hitachi</t>
-        </is>
+      <c r="A14" t="n">
+        <v>405283</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>123</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.328751000157634</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -678,16 +664,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1195062105462084</v>
+        <v>-0.02884368962540955</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BGH</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -696,16 +682,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="D16" t="n">
-        <v>0.660668652045552</v>
+        <v>0.09409074071364756</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Enova</t>
+          <t>Noblex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -714,14 +700,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>286</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5351674244892505</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tedge</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -730,14 +718,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>198</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2493554940964689</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>Telefunken</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -746,16 +736,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1892600538008133</v>
+        <v>-0.7818948450812683</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Feelnology</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -764,14 +754,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9800252943286722</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>BGH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -780,16 +772,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>1.155834493391884</v>
+        <v>0.8066777860527927</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -798,14 +790,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.123557968712633</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Philco</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -814,16 +808,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D23" t="n">
-        <v>1.406208517972415</v>
+        <v>1.251368687162552</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Feelnology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -832,16 +826,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>70</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.106942236705434</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hisense</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -850,16 +842,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1357022130817121</v>
+        <v>-0.05268619565576848</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>Philco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -868,14 +860,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7674421603918532</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>Kanji</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -884,16 +878,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2212715241358621</v>
+        <v>-1.24500794543324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quint</t>
+          <t>Candy</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -902,14 +896,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JVC</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -918,16 +912,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.811736910415498</v>
+        <v>0.1196019463005934</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sanyo</t>
+          <t>Enova</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -936,16 +930,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.239470443791885</v>
+        <v>-1.072176975494282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kanji</t>
+          <t>Tedge</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -954,16 +948,14 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-1.25393521133709</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Admiral</t>
+          <t>Hisense</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -972,16 +964,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.587261070548225</v>
+        <v>1.088007927050524</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kodak</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -990,16 +982,14 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-1.813798030320057</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Quint</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1008,14 +998,14 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Skyworth</t>
+          <t>Sanyo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1024,14 +1014,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-1.787969880649163</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hyundai Electronics</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1047,7 +1039,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Top House</t>
+          <t>Skyworth</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1063,369 +1055,397 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Admiral</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>23</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.974702170128014</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>JVC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>61</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.07201372723184041</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Genérico</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Top House</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Talent</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hyundai Electronics</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Steel Home</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>CMB</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>812.8</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1148</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.325376379680352</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1270</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>935</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.9854277527009757</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>609.5999999999999</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>153</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-1.185259289103636</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1092.2</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>775</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.8717397059260841</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1397</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>241</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.8498665709890004</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1066.8</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>90</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-1.329799537453058</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>990.5999999999999</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>26</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1651</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>50</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1016</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>178</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.5173515827397187</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1524</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1778</v>
-      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>1473.2</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EZ-Pro Screen Protector</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>1905</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>au optronics</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>Tizen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1152</v>
+        <v>209</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.105997607225658</v>
+        <v>0.94538314248573</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4K</t>
+          <t>Saphi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1251</v>
+        <v>194</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8403608915930291</v>
+        <v>-2.086547122841317</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full HD</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>876</v>
+        <v>110</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2656367156326264</v>
+        <v>0.1183794549328918</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4K UHD</t>
+          <t>Android TV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>949</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.633762705517082</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1366x768</t>
+          <t>Android Oreo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.7734741568908777</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1366 x 768 px</t>
+          <t>Android Pie</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.4468300678039809</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FHD</t>
+          <t>Android 10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.1887729321656027</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UHD</t>
+          <t>webOS 6.0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.1284034436520753</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HD ready</t>
+          <t>webOS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tipo de resolución</t>
+          <t>Sistema operativo</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.194337342852064</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tizen</t>
+          <t>Android KitKat</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1434,16 +1454,14 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>141</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.9225320911808448</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Saphi</t>
+          <t>webOS 4.0</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1452,16 +1470,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.924122208415359</v>
+        <v>-0.4261085505115406</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Android 10</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1470,16 +1488,14 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>41</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-0.3435489611394745</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Android TV</t>
+          <t>Xmart UI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1488,16 +1504,14 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>716</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.693702176774144</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Vidaa</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1506,137 +1520,123 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>78</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.2272438938875703</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>webOS 6.0</t>
-        </is>
+      <c r="A66" t="n">
+        <v>11.85</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0593820952965738</v>
+        <v>1.263798068863654</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>webOS 4.0</t>
-        </is>
+      <c r="A67" t="n">
+        <v>5.425000000000001</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.3624214799073424</v>
+        <v>0.3429348670143393</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Android Oreo</t>
-        </is>
+      <c r="A68" t="n">
+        <v>2.05</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D68" t="n">
-        <v>1.001015270956938</v>
+        <v>-0.5069414347516309</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>webOS</t>
-        </is>
+      <c r="A69" t="n">
+        <v>9.649999999999999</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.2359924829377555</v>
+        <v>0.356051604815716</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Xmart UI</t>
-        </is>
+      <c r="A70" t="n">
+        <v>14.6</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>14</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.8396561603323403</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Android Pie</t>
-        </is>
+      <c r="A71" t="n">
+        <v>7.550000000000001</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.4645384173278526</v>
+        <v>0.9179942302181426</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Android</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20.95</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sistema operativo</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>12.6</v>
+        <v>17.9</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1644,15 +1644,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>24</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.2310754830078264</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3.4</v>
+        <v>26.9</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1660,15 +1658,15 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.71370367242568</v>
+        <v>-1.534181175827881</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>7.75</v>
+        <v>33.7</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1676,179 +1674,659 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>30</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.4381082511161873</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5.575</v>
+        <v>1257.3</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>55</v>
+        <v>1233</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8670039470360807</v>
+        <v>0.5541521331001807</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10.05</v>
+        <v>1079.5</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50</v>
+        <v>1090</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8448146290961597</v>
+        <v>0.5054889332494115</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>22.1</v>
+        <v>774.6999999999999</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>1334</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.667298637830574</v>
+        <v>0.06136218866720463</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>16.55</v>
+        <v>1003.3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>309</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.5845909952990777</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>20</v>
+        <v>1397</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Potencia máxima de los parlantes</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>443</v>
+        <v>520</v>
       </c>
       <c r="D80" t="n">
-        <v>0.7760802674832891</v>
+        <v>1.136787703859346</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16</v>
+        <v>609.5999999999999</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Potencia máxima de los parlantes</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>730</v>
+        <v>155</v>
       </c>
       <c r="D81" t="n">
-        <v>0.5908421040603133</v>
+        <v>-1.673199963577065</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>10</v>
+        <v>1587.5</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Potencia máxima de los parlantes</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>330</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.06298594617374244</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>19</v>
+        <v>1841.5</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Potencia máxima de los parlantes</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>46</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-1.429908317717345</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>12</v>
+        <v>2209.8</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Potencia máxima de los parlantes</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>18</v>
+        <v>1485.9</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Potencia máxima de los parlantes</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
+        <v>1206.5</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.9811830988002536</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full HD</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1141</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.03662737568844757</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1313</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-1.017810474488698</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3840 x 2160 px</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1921 x 1080 px</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1366 x 768 px</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4K UHD</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>8K</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>QLED</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1366x768</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>UHD</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HD ready</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3,840 x 2,160</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SMART TV</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tipo de resolución</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>20</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>650</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.166031580515335</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>16</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.9987277264316294</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>10</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>383</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.4854739862995862</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>19</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>50</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.6737988561031819</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>6</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>50</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-0.9820184414771076</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>12</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>32</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
         <v>15</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C111" t="n">
         <v>1</v>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>59</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-0.9944159956662617</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>40</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>10</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>14</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>33</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>18</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>35</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Potencia máxima de los parlantes</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/modelling/atribucion/tv/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/tv/df_attr_values_sent.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,1908 +425,2256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_opi_con_sent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>sent</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>106999</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>113</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.8701611836201959</v>
+      <c r="E2" t="n">
+        <v>0.4213801718450114</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>65739</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>266</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.849566187897854</v>
+      <c r="E3" t="n">
+        <v>0.760134186501937</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
         <v>38468.5</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>337</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.3838895285317757</v>
+      <c r="E4" t="n">
+        <v>0.6684046248836704</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
         <v>53048.5</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>339</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.3459012026978988</v>
+      <c r="E5" t="n">
+        <v>0.6609216376966015</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
         <v>80849</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>248</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.7479914263107726</v>
+      <c r="E6" t="n">
+        <v>0.7401258649241568</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
         <v>92911</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>286</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.7049315310858165</v>
+      <c r="E7" t="n">
+        <v>0.73164387375524</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
         <v>129994.5</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>76</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.7652905704200198</v>
+      <c r="E8" t="n">
+        <v>0.7435334716263535</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
         <v>17561</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>143</v>
       </c>
-      <c r="D9" t="n">
-        <v>-0.6171398473742488</v>
+      <c r="E9" t="n">
+        <v>0.4712206261325501</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
         <v>45400</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>242</v>
       </c>
-      <c r="D10" t="n">
-        <v>-0.02323040065098755</v>
+      <c r="E10" t="n">
+        <v>0.5882096400613004</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
         <v>159499</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>39</v>
       </c>
-      <c r="D11" t="n">
-        <v>-2.287039015298706</v>
+      <c r="E11" t="n">
+        <v>0.1422818323589045</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
         <v>212499.5</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
         <v>324999.5</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
         <v>405283</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>148</v>
       </c>
-      <c r="D15" t="n">
-        <v>-0.02884368962540955</v>
+      <c r="E15" t="n">
+        <v>0.5356964984097136</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>217</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.09409074071364756</v>
+      <c r="E16" t="n">
+        <v>0.5594452393806584</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Noblex</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>286</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.5351674244892505</v>
+      <c r="E17" t="n">
+        <v>0.6446533936985309</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>TCL</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>198</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.2493554940964689</v>
+      <c r="E18" t="n">
+        <v>0.5894396225639248</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Telefunken</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>52</v>
       </c>
-      <c r="D19" t="n">
-        <v>-0.7818948450812683</v>
+      <c r="E19" t="n">
+        <v>0.3902204362563592</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>RCA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>248</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.9800252943286722</v>
+      <c r="E20" t="n">
+        <v>0.7305920057746158</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>BGH</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>112</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.8066777860527927</v>
+      <c r="E21" t="n">
+        <v>0.6971043566217434</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Hitachi</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>209</v>
       </c>
-      <c r="D22" t="n">
-        <v>1.123557968712633</v>
+      <c r="E22" t="n">
+        <v>0.7583199603875772</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Hyundai</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>99</v>
       </c>
-      <c r="D23" t="n">
-        <v>1.251368687162552</v>
+      <c r="E23" t="n">
+        <v>0.7830107133150193</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Feelnology</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>8</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>69</v>
       </c>
-      <c r="D25" t="n">
-        <v>-0.05268619565576848</v>
+      <c r="E25" t="n">
+        <v>0.5310905511722187</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Philco</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>89</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.7674421603918532</v>
+      <c r="E26" t="n">
+        <v>0.6895247330119485</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Kanji</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>52</v>
       </c>
-      <c r="D27" t="n">
-        <v>-1.24500794543324</v>
+      <c r="E27" t="n">
+        <v>0.3007552389948895</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Candy</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>13</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>AOC</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>70</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.1196019463005934</v>
+      <c r="E29" t="n">
+        <v>0.5643735496324724</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Enova</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>37</v>
       </c>
-      <c r="D30" t="n">
-        <v>-1.072176975494282</v>
+      <c r="E30" t="n">
+        <v>0.3341431021469542</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Tedge</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>14</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Hisense</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>91</v>
       </c>
-      <c r="D32" t="n">
-        <v>1.088007927050524</v>
+      <c r="E32" t="n">
+        <v>0.7514523259208847</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Xiaomi</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>Quint</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Sanyo</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>21</v>
       </c>
-      <c r="D35" t="n">
-        <v>-1.787969880649163</v>
+      <c r="E35" t="n">
+        <v>0.195864669925167</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Skyworth</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Admiral</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>23</v>
       </c>
-      <c r="D38" t="n">
-        <v>-1.974702170128014</v>
+      <c r="E38" t="n">
+        <v>0.1597913195910596</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>JVC</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>61</v>
       </c>
-      <c r="D39" t="n">
-        <v>-0.07201372723184041</v>
+      <c r="E39" t="n">
+        <v>0.5273568165322001</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Genérico</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Motorola</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Top House</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Talent</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>CMA</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Hyundai Electronics</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Zenith</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Steel Home</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Kodak</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>CMB</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>EZ-Pro Screen Protector</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>au optronics</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Tizen</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>209</v>
       </c>
-      <c r="D52" t="n">
-        <v>0.94538314248573</v>
+      <c r="E52" t="n">
+        <v>0.3943034176685986</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Saphi</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>194</v>
       </c>
-      <c r="D53" t="n">
-        <v>-2.086547122841317</v>
+      <c r="E53" t="n">
+        <v>-0.1757006979445402</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Linux</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>110</v>
       </c>
-      <c r="D54" t="n">
-        <v>0.1183794549328918</v>
+      <c r="E54" t="n">
+        <v>0.2388263900722823</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Android TV</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>949</v>
       </c>
-      <c r="D55" t="n">
-        <v>1.633762705517082</v>
+      <c r="E55" t="n">
+        <v>0.5237190538126969</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Android Oreo</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>121</v>
       </c>
-      <c r="D56" t="n">
-        <v>0.7734741568908777</v>
+      <c r="E56" t="n">
+        <v>0.3619844588783721</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Android Pie</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>45</v>
       </c>
-      <c r="D57" t="n">
-        <v>-0.4468300678039809</v>
+      <c r="E57" t="n">
+        <v>0.1325667712980347</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Android 10</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>48</v>
       </c>
-      <c r="D58" t="n">
-        <v>-0.1887729321656027</v>
+      <c r="E58" t="n">
+        <v>0.1810816171239319</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>webOS 6.0</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>44</v>
       </c>
-      <c r="D59" t="n">
-        <v>-0.1284034436520753</v>
+      <c r="E59" t="n">
+        <v>0.1924311053703112</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>webOS</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>43</v>
       </c>
-      <c r="D60" t="n">
-        <v>-0.194337342852064</v>
+      <c r="E60" t="n">
+        <v>0.1800355056653287</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Android KitKat</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>2</v>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>webOS 4.0</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>33</v>
       </c>
-      <c r="D62" t="n">
-        <v>-0.4261085505115406</v>
+      <c r="E62" t="n">
+        <v>0.1364624249261915</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>Android</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>11</v>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Xmart UI</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>14</v>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Vidaa</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Sistema operativo</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B66" t="n">
         <v>11.85</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>47</v>
       </c>
-      <c r="D66" t="n">
-        <v>1.263798068863654</v>
+      <c r="E66" t="n">
+        <v>0.725538222372787</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="n">
         <v>5.425000000000001</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>68</v>
       </c>
-      <c r="D67" t="n">
-        <v>0.3429348670143393</v>
+      <c r="E67" t="n">
+        <v>0.5332555405669315</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" t="n">
         <v>2.05</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>88</v>
       </c>
-      <c r="D68" t="n">
-        <v>-0.5069414347516309</v>
+      <c r="E68" t="n">
+        <v>0.355795420346443</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" t="n">
         <v>9.649999999999999</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>52</v>
       </c>
-      <c r="D69" t="n">
-        <v>0.356051604815716</v>
+      <c r="E69" t="n">
+        <v>0.5359944072258749</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" t="n">
         <v>14.6</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>15</v>
       </c>
-      <c r="D70" t="n">
-        <v>-0.8396561603323403</v>
+      <c r="E70" t="n">
+        <v>0.286322256924905</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B71" t="n">
         <v>7.550000000000001</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>42</v>
       </c>
-      <c r="D71" t="n">
-        <v>0.9179942302181426</v>
+      <c r="E71" t="n">
+        <v>0.6533319605306522</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B72" t="n">
         <v>20.95</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>6</v>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B73" t="n">
         <v>17.9</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>5</v>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B74" t="n">
         <v>26.9</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>7</v>
       </c>
-      <c r="D74" t="n">
-        <v>-1.534181175827881</v>
+      <c r="E74" t="n">
+        <v>0.1413005726046442</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B75" t="n">
         <v>33.7</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>4</v>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B76" t="n">
         <v>1257.3</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>1233</v>
       </c>
-      <c r="D76" t="n">
-        <v>0.5541521331001807</v>
+      <c r="E76" t="n">
+        <v>0.5899492914048396</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="n">
         <v>1079.5</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>1090</v>
       </c>
-      <c r="D77" t="n">
-        <v>0.5054889332494115</v>
+      <c r="E77" t="n">
+        <v>0.5717718635479183</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" t="n">
         <v>774.6999999999999</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>1334</v>
       </c>
-      <c r="D78" t="n">
-        <v>0.06136218866720463</v>
+      <c r="E78" t="n">
+        <v>0.4382422402014789</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" t="n">
         <v>1003.3</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>309</v>
       </c>
-      <c r="D79" t="n">
-        <v>-0.5845909952990777</v>
+      <c r="E79" t="n">
+        <v>0.4005570645282683</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="n">
         <v>1397</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>520</v>
       </c>
-      <c r="D80" t="n">
-        <v>1.136787703859346</v>
+      <c r="E80" t="n">
+        <v>0.7725075403666801</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B81" t="n">
         <v>609.5999999999999</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>155</v>
       </c>
-      <c r="D81" t="n">
-        <v>-1.673199963577065</v>
+      <c r="E81" t="n">
+        <v>0.1347067297289372</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B82" t="n">
         <v>1587.5</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>96</v>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B83" t="n">
         <v>1841.5</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>26</v>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B84" t="n">
         <v>2209.8</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>7</v>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B85" t="n">
         <v>1485.9</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>51</v>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B86" t="n">
         <v>1206.5</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B87" t="n">
         <v>2032</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>4K</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>1850</v>
       </c>
-      <c r="D88" t="n">
-        <v>0.9811830988002536</v>
+      <c r="E88" t="n">
+        <v>0.7809909017751145</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>Full HD</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>1141</v>
       </c>
-      <c r="D89" t="n">
-        <v>0.03662737568844757</v>
+      <c r="E89" t="n">
+        <v>0.7376914049461211</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>1313</v>
       </c>
-      <c r="D90" t="n">
-        <v>-1.017810474488698</v>
+      <c r="E90" t="n">
+        <v>0.6893547878117694</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>3840 x 2160 px</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>1921 x 1080 px</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>1366 x 768 px</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>4K UHD</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>2</v>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>8K</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>QLED</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>1366x768</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>UHD</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>HD ready</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>1920x1080</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>3,840 x 2,160</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>SMART TV</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Tipo de resolución</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B104" t="n">
         <v>20</v>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>650</v>
       </c>
-      <c r="D104" t="n">
-        <v>1.166031580515335</v>
+      <c r="E104" t="n">
+        <v>0.7128334186937576</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B105" t="n">
         <v>16</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>1013</v>
       </c>
-      <c r="D105" t="n">
-        <v>0.9987277264316294</v>
+      <c r="E105" t="n">
+        <v>0.662414225987358</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B106" t="n">
         <v>10</v>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>383</v>
       </c>
-      <c r="D106" t="n">
-        <v>0.4854739862995862</v>
+      <c r="E106" t="n">
+        <v>0.5077385350253879</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" t="n">
         <v>19</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>50</v>
       </c>
-      <c r="D107" t="n">
-        <v>-0.6737988561031819</v>
+      <c r="E107" t="n">
+        <v>0.1583765842172666</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B108" t="n">
         <v>6</v>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>50</v>
       </c>
-      <c r="D108" t="n">
-        <v>-0.9820184414771076</v>
+      <c r="E108" t="n">
+        <v>0.06549060286336757</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B109" t="n">
         <v>12</v>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>32</v>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B110" t="n">
         <v>9.5</v>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B111" t="n">
         <v>15</v>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>1</v>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" t="n">
+        <v>8</v>
+      </c>
+      <c r="C112" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>59</v>
       </c>
-      <c r="D112" t="n">
-        <v>-0.9944159956662617</v>
+      <c r="E112" t="n">
+        <v>0.06175443864184134</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B113" t="n">
         <v>40</v>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>10</v>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B114" t="n">
         <v>5</v>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B115" t="n">
         <v>14</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="D115" t="n">
         <v>33</v>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B116" t="n">
         <v>18</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>35</v>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B117" t="n">
         <v>4</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Potencia máxima de los parlantes</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
